--- a/data/excel/skills.xlsx
+++ b/data/excel/skills.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Skills'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Skills'!$A$1:$M$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -438,22 +439,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,7 +490,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>范围/射程</t>
+          <t>范围</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -509,7 +510,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>命中BuffID</t>
+          <t>命中Buff</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -519,245 +520,396 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>自身BuffID</t>
+          <t>自身Buff</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>普攻</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>melee</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="n">
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>火球术</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>projectile</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>skill1</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/fireball.tscn</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="n">
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>2001</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>旋风斩</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>aoe</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>skill2</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>1005</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>冰霜箭</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>penetrate</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>skill3</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/frost_arrow.tscn</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="n">
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
         <v>1003</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>全屏斩</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>fullscreen</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>skill2</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="n">
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>毒液攻击</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1001</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>酸液喷射</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>projectile</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>skill1</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1001</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>毒雾爆发</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>aoe</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>skill2</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>1001</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/skills.xlsx
+++ b/data/excel/skills.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rc21c19513d2c4d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R0b8c541092ec4532"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -50,7 +50,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -58,6 +58,12 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -363,6 +369,8 @@
     <x:col min="11" max="11" width="16" customWidth="1"/>
     <x:col min="12" max="12" width="16" customWidth="1"/>
     <x:col min="13" max="13" width="16" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -431,8 +439,14 @@
           <x:t xml:space="preserve">自身Buff</x:t>
         </x:is>
       </x:c>
+      <x:c r="N1" t="str">
+        <x:v>生效时机</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>作用说明</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1001</x:t>
@@ -482,8 +496,14 @@
       <x:c r="M2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N2" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O2" s="5" t="str">
+        <x:v>近战普通攻击；有效帧命中目标时造成1.0倍伤害。</x:v>
+      </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1002</x:t>
@@ -533,8 +553,14 @@
       <x:c r="M3" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N3" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O3" s="5" t="str">
+        <x:v>有效帧发射火球；命中造成1.5倍伤害，并必定附加Buff 2001。</x:v>
+      </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1003</x:t>
@@ -584,8 +610,14 @@
       <x:c r="M4" s="3" t="n">
         <x:v>1005</x:v>
       </x:c>
+      <x:c r="N4" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O4" s="5" t="str">
+        <x:v>有效帧对自身周围80半径造成2.0倍伤害，并为自身附加Buff 1005。</x:v>
+      </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1004</x:t>
@@ -635,8 +667,14 @@
       <x:c r="M5" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N5" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O5" s="5" t="str">
+        <x:v>有效帧发射无限穿透冰霜箭；造成1.2倍伤害，50%概率附加Buff 1003。</x:v>
+      </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1005</x:t>
@@ -686,8 +724,14 @@
       <x:c r="M6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N6" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O6" s="5" t="str">
+        <x:v>有效帧对全场敌方目标造成3.0倍伤害。</x:v>
+      </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2001</x:t>
@@ -737,8 +781,14 @@
       <x:c r="M7" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N7" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O7" s="5" t="str">
+        <x:v>60范围近战攻击；造成1.0倍伤害，30%概率附加Buff 1001。</x:v>
+      </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="32" customHeight="1">
       <x:c r="A8" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2002</x:t>
@@ -788,8 +838,14 @@
       <x:c r="M8" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N8" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O8" s="5" t="str">
+        <x:v>200范围酸液投射；造成1.5倍伤害，50%概率附加Buff 1001；当前弹道场景为空。</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2003</x:t>
@@ -839,8 +895,19 @@
       <x:c r="M9" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N9" t="str">
+        <x:v>active_frame</x:v>
+      </x:c>
+      <x:c r="O9" s="5" t="str">
+        <x:v>有效帧对自身周围60半径造成2.0倍伤害，命中必定附加Buff 1001。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="N2:N9">
+      <x:formula1>"cast_start,active_frame,animation_end"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>